--- a/AAII_Financials/Yearly/SRG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SRG_YR_FIN.xlsx
@@ -2973,7 +2973,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="E60" s="3">
         <v>29700</v>
@@ -3126,7 +3126,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>48300</v>
+        <v>48100</v>
       </c>
       <c r="E61" s="3">
         <v>241200</v>
